--- a/content/resume_template.xlsx
+++ b/content/resume_template.xlsx
@@ -9,12 +9,12 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_resume_map" sheetId="1" state="hidden" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Page 1 - Experience" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Page 2 - Portfolio" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resume" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portfolio" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Page 1 - Experience'!$A$1:$H$42</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Page 2 - Portfolio'!$A$1:$H$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Resume'!$A$1:$H$102</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Portfolio'!$A$1:$H$65</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -323,109 +323,299 @@
         <t>bullet: edit text here; resize merged range if this content needs more or less room.</t>
       </text>
     </comment>
-    <comment ref="A14" authorId="0" shapeId="0">
+    <comment ref="A15" authorId="0" shapeId="0">
+      <text>
+        <t>role: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="E15" authorId="0" shapeId="0">
+      <text>
+        <t>dates: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A16" authorId="0" shapeId="0">
+      <text>
+        <t>organization: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="E16" authorId="0" shapeId="0">
+      <text>
+        <t>location: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A17" authorId="0" shapeId="0">
       <text>
         <t>bullet: edit text here; resize merged range if this content needs more or less room.</t>
       </text>
     </comment>
-    <comment ref="A17" authorId="0" shapeId="0">
+    <comment ref="A21" authorId="0" shapeId="0">
+      <text>
+        <t>section_heading: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A22" authorId="0" shapeId="0">
+      <text>
+        <t>skill_label: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="C22" authorId="0" shapeId="0">
+      <text>
+        <t>skill_items: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A25" authorId="0" shapeId="0">
+      <text>
+        <t>section_heading: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A26" authorId="0" shapeId="0">
       <text>
         <t>role: edit text here; resize merged range if this content needs more or less room.</t>
       </text>
     </comment>
-    <comment ref="E17" authorId="0" shapeId="0">
+    <comment ref="E26" authorId="0" shapeId="0">
       <text>
         <t>dates: edit text here; resize merged range if this content needs more or less room.</t>
       </text>
     </comment>
-    <comment ref="A18" authorId="0" shapeId="0">
+    <comment ref="A27" authorId="0" shapeId="0">
       <text>
         <t>organization: edit text here; resize merged range if this content needs more or less room.</t>
       </text>
     </comment>
-    <comment ref="E18" authorId="0" shapeId="0">
+    <comment ref="E27" authorId="0" shapeId="0">
       <text>
         <t>location: edit text here; resize merged range if this content needs more or less room.</t>
       </text>
     </comment>
-    <comment ref="A19" authorId="0" shapeId="0">
+    <comment ref="A28" authorId="0" shapeId="0">
       <text>
         <t>bullet: edit text here; resize merged range if this content needs more or less room.</t>
       </text>
     </comment>
-    <comment ref="A21" authorId="0" shapeId="0">
+    <comment ref="A31" authorId="0" shapeId="0">
+      <text>
+        <t>role: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="E31" authorId="0" shapeId="0">
+      <text>
+        <t>dates: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A32" authorId="0" shapeId="0">
+      <text>
+        <t>organization: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="E32" authorId="0" shapeId="0">
+      <text>
+        <t>location: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A33" authorId="0" shapeId="0">
       <text>
         <t>bullet: edit text here; resize merged range if this content needs more or less room.</t>
       </text>
     </comment>
-    <comment ref="A25" authorId="0" shapeId="0">
+    <comment ref="A36" authorId="0" shapeId="0">
+      <text>
+        <t>role: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="E36" authorId="0" shapeId="0">
+      <text>
+        <t>dates: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A37" authorId="0" shapeId="0">
+      <text>
+        <t>organization: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="E37" authorId="0" shapeId="0">
+      <text>
+        <t>location: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A38" authorId="0" shapeId="0">
+      <text>
+        <t>bullet: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A40" authorId="0" shapeId="0">
+      <text>
+        <t>bullet: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A42" authorId="0" shapeId="0">
+      <text>
+        <t>bullet: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A44" authorId="0" shapeId="0">
+      <text>
+        <t>bullet: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A46" authorId="0" shapeId="0">
+      <text>
+        <t>bullet: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A48" authorId="0" shapeId="0">
+      <text>
+        <t>bullet: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A50" authorId="0" shapeId="0">
+      <text>
+        <t>bullet: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A52" authorId="0" shapeId="0">
+      <text>
+        <t>bullet: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A55" authorId="0" shapeId="0">
+      <text>
+        <t>role: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="E55" authorId="0" shapeId="0">
+      <text>
+        <t>dates: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A56" authorId="0" shapeId="0">
+      <text>
+        <t>organization: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="E56" authorId="0" shapeId="0">
+      <text>
+        <t>location: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A57" authorId="0" shapeId="0">
+      <text>
+        <t>bullet: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A59" authorId="0" shapeId="0">
+      <text>
+        <t>bullet: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A61" authorId="0" shapeId="0">
+      <text>
+        <t>bullet: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A63" authorId="0" shapeId="0">
+      <text>
+        <t>bullet: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A66" authorId="0" shapeId="0">
+      <text>
+        <t>role: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="E66" authorId="0" shapeId="0">
+      <text>
+        <t>dates: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A67" authorId="0" shapeId="0">
+      <text>
+        <t>organization: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="E67" authorId="0" shapeId="0">
+      <text>
+        <t>location: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A68" authorId="0" shapeId="0">
+      <text>
+        <t>bullet: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A70" authorId="0" shapeId="0">
+      <text>
+        <t>bullet: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A72" authorId="0" shapeId="0">
+      <text>
+        <t>bullet: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A76" authorId="0" shapeId="0">
       <text>
         <t>section_heading: edit text here; resize merged range if this content needs more or less room.</t>
       </text>
     </comment>
-    <comment ref="A26" authorId="0" shapeId="0">
-      <text>
-        <t>skill_label: edit text here; resize merged range if this content needs more or less room.</t>
-      </text>
-    </comment>
-    <comment ref="C26" authorId="0" shapeId="0">
-      <text>
-        <t>skill_items: edit text here; resize merged range if this content needs more or less room.</t>
-      </text>
-    </comment>
-    <comment ref="A28" authorId="0" shapeId="0">
-      <text>
-        <t>skill_label: edit text here; resize merged range if this content needs more or less room.</t>
-      </text>
-    </comment>
-    <comment ref="C28" authorId="0" shapeId="0">
-      <text>
-        <t>skill_items: edit text here; resize merged range if this content needs more or less room.</t>
-      </text>
-    </comment>
-    <comment ref="A30" authorId="0" shapeId="0">
-      <text>
-        <t>skill_label: edit text here; resize merged range if this content needs more or less room.</t>
-      </text>
-    </comment>
-    <comment ref="C30" authorId="0" shapeId="0">
-      <text>
-        <t>skill_items: edit text here; resize merged range if this content needs more or less room.</t>
-      </text>
-    </comment>
-    <comment ref="A33" authorId="0" shapeId="0">
+    <comment ref="A77" authorId="0" shapeId="0">
+      <text>
+        <t>list_item: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A80" authorId="0" shapeId="0">
       <text>
         <t>section_heading: edit text here; resize merged range if this content needs more or less room.</t>
       </text>
     </comment>
-    <comment ref="A34" authorId="0" shapeId="0">
-      <text>
-        <t>role: edit text here; resize merged range if this content needs more or less room.</t>
-      </text>
-    </comment>
-    <comment ref="E34" authorId="0" shapeId="0">
-      <text>
-        <t>dates: edit text here; resize merged range if this content needs more or less room.</t>
-      </text>
-    </comment>
-    <comment ref="A35" authorId="0" shapeId="0">
-      <text>
-        <t>organization: edit text here; resize merged range if this content needs more or less room.</t>
-      </text>
-    </comment>
-    <comment ref="E35" authorId="0" shapeId="0">
-      <text>
-        <t>location: edit text here; resize merged range if this content needs more or less room.</t>
-      </text>
-    </comment>
-    <comment ref="A36" authorId="0" shapeId="0">
-      <text>
-        <t>bullet: edit text here; resize merged range if this content needs more or less room.</t>
-      </text>
-    </comment>
-    <comment ref="A38" authorId="0" shapeId="0">
-      <text>
-        <t>bullet: edit text here; resize merged range if this content needs more or less room.</t>
+    <comment ref="A81" authorId="0" shapeId="0">
+      <text>
+        <t>list_item: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A83" authorId="0" shapeId="0">
+      <text>
+        <t>list_item: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A85" authorId="0" shapeId="0">
+      <text>
+        <t>list_item: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A87" authorId="0" shapeId="0">
+      <text>
+        <t>list_item: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A90" authorId="0" shapeId="0">
+      <text>
+        <t>section_heading: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A91" authorId="0" shapeId="0">
+      <text>
+        <t>list_item: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A93" authorId="0" shapeId="0">
+      <text>
+        <t>list_item: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A95" authorId="0" shapeId="0">
+      <text>
+        <t>list_item: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A98" authorId="0" shapeId="0">
+      <text>
+        <t>section_heading: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A99" authorId="0" shapeId="0">
+      <text>
+        <t>list_item: edit text here; resize merged range if this content needs more or less room.</t>
       </text>
     </comment>
   </commentList>
@@ -493,72 +683,212 @@
         <t>bullet: edit text here; resize merged range if this content needs more or less room.</t>
       </text>
     </comment>
-    <comment ref="A14" authorId="0" shapeId="0">
+    <comment ref="A15" authorId="0" shapeId="0">
+      <text>
+        <t>role: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="E15" authorId="0" shapeId="0">
+      <text>
+        <t>dates: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A16" authorId="0" shapeId="0">
+      <text>
+        <t>organization: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="E16" authorId="0" shapeId="0">
+      <text>
+        <t>location: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A17" authorId="0" shapeId="0">
       <text>
         <t>bullet: edit text here; resize merged range if this content needs more or less room.</t>
       </text>
     </comment>
-    <comment ref="A17" authorId="0" shapeId="0">
+    <comment ref="A19" authorId="0" shapeId="0">
+      <text>
+        <t>bullet: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A22" authorId="0" shapeId="0">
       <text>
         <t>role: edit text here; resize merged range if this content needs more or less room.</t>
       </text>
     </comment>
-    <comment ref="E17" authorId="0" shapeId="0">
+    <comment ref="E22" authorId="0" shapeId="0">
       <text>
         <t>dates: edit text here; resize merged range if this content needs more or less room.</t>
       </text>
     </comment>
-    <comment ref="A18" authorId="0" shapeId="0">
+    <comment ref="A23" authorId="0" shapeId="0">
       <text>
         <t>organization: edit text here; resize merged range if this content needs more or less room.</t>
       </text>
     </comment>
-    <comment ref="E18" authorId="0" shapeId="0">
+    <comment ref="E23" authorId="0" shapeId="0">
       <text>
         <t>location: edit text here; resize merged range if this content needs more or less room.</t>
       </text>
     </comment>
-    <comment ref="A19" authorId="0" shapeId="0">
+    <comment ref="A24" authorId="0" shapeId="0">
       <text>
         <t>bullet: edit text here; resize merged range if this content needs more or less room.</t>
       </text>
     </comment>
-    <comment ref="A21" authorId="0" shapeId="0">
+    <comment ref="A26" authorId="0" shapeId="0">
       <text>
         <t>bullet: edit text here; resize merged range if this content needs more or less room.</t>
       </text>
     </comment>
-    <comment ref="A25" authorId="0" shapeId="0">
+    <comment ref="A29" authorId="0" shapeId="0">
+      <text>
+        <t>role: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="E29" authorId="0" shapeId="0">
+      <text>
+        <t>dates: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A30" authorId="0" shapeId="0">
+      <text>
+        <t>organization: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="E30" authorId="0" shapeId="0">
+      <text>
+        <t>location: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A31" authorId="0" shapeId="0">
+      <text>
+        <t>bullet: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A33" authorId="0" shapeId="0">
+      <text>
+        <t>bullet: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A36" authorId="0" shapeId="0">
+      <text>
+        <t>role: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="E36" authorId="0" shapeId="0">
+      <text>
+        <t>dates: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A37" authorId="0" shapeId="0">
+      <text>
+        <t>organization: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="E37" authorId="0" shapeId="0">
+      <text>
+        <t>location: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A38" authorId="0" shapeId="0">
+      <text>
+        <t>bullet: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A40" authorId="0" shapeId="0">
+      <text>
+        <t>bullet: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A44" authorId="0" shapeId="0">
       <text>
         <t>section_heading: edit text here; resize merged range if this content needs more or less room.</t>
       </text>
     </comment>
-    <comment ref="A26" authorId="0" shapeId="0">
+    <comment ref="A45" authorId="0" shapeId="0">
       <text>
         <t>role: edit text here; resize merged range if this content needs more or less room.</t>
       </text>
     </comment>
-    <comment ref="E26" authorId="0" shapeId="0">
+    <comment ref="E45" authorId="0" shapeId="0">
       <text>
         <t>dates: edit text here; resize merged range if this content needs more or less room.</t>
       </text>
     </comment>
-    <comment ref="A27" authorId="0" shapeId="0">
+    <comment ref="A46" authorId="0" shapeId="0">
       <text>
         <t>organization: edit text here; resize merged range if this content needs more or less room.</t>
       </text>
     </comment>
-    <comment ref="E27" authorId="0" shapeId="0">
+    <comment ref="E46" authorId="0" shapeId="0">
       <text>
         <t>location: edit text here; resize merged range if this content needs more or less room.</t>
       </text>
     </comment>
-    <comment ref="A28" authorId="0" shapeId="0">
+    <comment ref="A47" authorId="0" shapeId="0">
       <text>
         <t>bullet: edit text here; resize merged range if this content needs more or less room.</t>
       </text>
     </comment>
-    <comment ref="A30" authorId="0" shapeId="0">
+    <comment ref="A49" authorId="0" shapeId="0">
+      <text>
+        <t>bullet: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A53" authorId="0" shapeId="0">
+      <text>
+        <t>section_heading: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A54" authorId="0" shapeId="0">
+      <text>
+        <t>role: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="E54" authorId="0" shapeId="0">
+      <text>
+        <t>dates: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A55" authorId="0" shapeId="0">
+      <text>
+        <t>organization: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="E55" authorId="0" shapeId="0">
+      <text>
+        <t>location: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A56" authorId="0" shapeId="0">
+      <text>
+        <t>bullet: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A59" authorId="0" shapeId="0">
+      <text>
+        <t>role: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="E59" authorId="0" shapeId="0">
+      <text>
+        <t>dates: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A60" authorId="0" shapeId="0">
+      <text>
+        <t>organization: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="E60" authorId="0" shapeId="0">
+      <text>
+        <t>location: edit text here; resize merged range if this content needs more or less room.</t>
+      </text>
+    </comment>
+    <comment ref="A61" authorId="0" shapeId="0">
       <text>
         <t>bullet: edit text here; resize merged range if this content needs more or less room.</t>
       </text>
@@ -856,7 +1186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H58"/>
+  <dimension ref="A1:H124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -904,7 +1234,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Page 1 - Experience</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -928,7 +1258,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Page 1 - Experience</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -952,7 +1282,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Page 1 - Experience</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -976,7 +1306,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Page 1 - Experience</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1000,7 +1330,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Page 1 - Experience</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1030,7 +1360,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Page 1 - Experience</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1062,7 +1392,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Page 1 - Experience</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1094,7 +1424,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Page 1 - Experience</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1126,7 +1456,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Page 1 - Experience</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1158,7 +1488,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Page 1 - Experience</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1190,7 +1520,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Page 1 - Experience</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1222,7 +1552,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Page 1 - Experience</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1238,23 +1568,23 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>bullet_2</t>
+          <t>role</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>A14</t>
+          <t>A15</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Page 1 - Experience</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1270,7 +1600,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>dates</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1279,14 +1609,14 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>A17</t>
+          <t>E15</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Page 1 - Experience</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1302,7 +1632,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>dates</t>
+          <t>organization</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1311,14 +1641,14 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>E17</t>
+          <t>A16</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Page 1 - Experience</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1334,7 +1664,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>organization</t>
+          <t>location</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1343,14 +1673,14 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>A18</t>
+          <t>E16</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Page 1 - Experience</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1366,7 +1696,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>bullet_0</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1375,78 +1705,76 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>E18</t>
+          <t>A17</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Page 1 - Experience</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>section</t>
+          <t>skills</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>bullet_0</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>1</v>
-      </c>
+          <t>block_heading</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>A19</t>
+          <t>A21</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Page 1 - Experience</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>section</t>
+          <t>skills</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>bullet_1</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" t="inlineStr"/>
+          <t>skill_label</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>A21</t>
+          <t>A22</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Page 1 - Experience</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1462,213 +1790,213 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>block_heading</t>
+          <t>skill_items</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>A25</t>
+          <t>C22</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Page 1 - Experience</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>skills</t>
+          <t>section</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>skill_label</t>
+          <t>block_heading</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>A26</t>
+          <t>A25</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Page 1 - Experience</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>skills</t>
+          <t>section</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>skill_items</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>C26</t>
+          <t>A26</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Page 1 - Experience</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>skills</t>
+          <t>section</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>skill_label</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="n">
-        <v>1</v>
-      </c>
+          <t>dates</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>A28</t>
+          <t>E26</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Page 1 - Experience</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>skills</t>
+          <t>section</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>skill_items</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="n">
-        <v>1</v>
-      </c>
+          <t>organization</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>C28</t>
+          <t>A27</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Page 1 - Experience</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>skills</t>
+          <t>section</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>skill_label</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="n">
-        <v>2</v>
-      </c>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>A30</t>
+          <t>E27</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Page 1 - Experience</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>skills</t>
+          <t>section</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>skill_items</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="n">
-        <v>2</v>
-      </c>
+          <t>bullet_0</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>C30</t>
+          <t>A28</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Page 1 - Experience</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1684,21 +2012,23 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>block_heading</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>A33</t>
+          <t>A31</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Page 1 - Experience</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1714,23 +2044,23 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>dates</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>A34</t>
+          <t>E31</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Page 1 - Experience</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1746,23 +2076,23 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>dates</t>
+          <t>organization</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>E34</t>
+          <t>A32</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Page 1 - Experience</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1778,23 +2108,23 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>organization</t>
+          <t>location</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>A35</t>
+          <t>E32</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Page 1 - Experience</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1810,23 +2140,23 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>bullet_0</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>E35</t>
+          <t>A33</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Page 1 - Experience</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1842,11 +2172,11 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>bullet_0</t>
+          <t>role</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
@@ -1858,7 +2188,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Page 1 - Experience</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1874,126 +2204,158 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>bullet_1</t>
+          <t>dates</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>A38</t>
+          <t>E36</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Page 2 - Portfolio</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="C34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
+          <t>organization</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>2</v>
+      </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A37</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Page 2 - Portfolio</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="C35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>headline</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>2</v>
+      </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>E37</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Page 2 - Portfolio</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>contact</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
+          <t>bullet_0</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>2</v>
+      </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>A38</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Page 2 - Portfolio</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="C37" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>page_title</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
+          <t>bullet_1</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>2</v>
+      </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>A40</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Page 2 - Portfolio</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2002,28 +2364,30 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>block_heading</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
+          <t>bullet_2</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>2</v>
+      </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>A7</t>
+          <t>A42</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Page 2 - Portfolio</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2032,30 +2396,30 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>bullet_3</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>A8</t>
+          <t>A44</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Page 2 - Portfolio</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -2064,30 +2428,30 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>dates</t>
+          <t>bullet_4</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>E8</t>
+          <t>A46</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Page 2 - Portfolio</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2096,30 +2460,30 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>organization</t>
+          <t>bullet_5</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>A9</t>
+          <t>A48</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Page 2 - Portfolio</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2128,30 +2492,30 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>bullet_6</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>E9</t>
+          <t>A50</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Page 2 - Portfolio</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -2160,30 +2524,30 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>bullet_0</t>
+          <t>bullet_7</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>A52</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Page 2 - Portfolio</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2192,30 +2556,30 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>bullet_1</t>
+          <t>role</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>A12</t>
+          <t>A55</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Page 2 - Portfolio</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2224,30 +2588,30 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>bullet_2</t>
+          <t>dates</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>A14</t>
+          <t>E55</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Page 2 - Portfolio</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -2256,30 +2620,30 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>organization</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>A17</t>
+          <t>A56</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Page 2 - Portfolio</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -2288,30 +2652,30 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>dates</t>
+          <t>location</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>E17</t>
+          <t>E56</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Page 2 - Portfolio</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2320,30 +2684,30 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>organization</t>
+          <t>bullet_0</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>A18</t>
+          <t>A57</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Page 2 - Portfolio</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2352,30 +2716,30 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>bullet_1</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>E18</t>
+          <t>A59</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Page 2 - Portfolio</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2384,30 +2748,30 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>bullet_0</t>
+          <t>bullet_2</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t>A19</t>
+          <t>A61</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Page 2 - Portfolio</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -2416,30 +2780,30 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>bullet_1</t>
+          <t>bullet_3</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
-          <t>A21</t>
+          <t>A63</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Page 2 - Portfolio</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -2448,28 +2812,30 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>block_heading</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>4</v>
+      </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
-          <t>A25</t>
+          <t>A66</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Page 2 - Portfolio</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -2478,30 +2844,30 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>dates</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>A26</t>
+          <t>E66</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Page 2 - Portfolio</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -2510,30 +2876,30 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>dates</t>
+          <t>organization</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>E26</t>
+          <t>A67</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Page 2 - Portfolio</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2542,30 +2908,30 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>organization</t>
+          <t>location</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>A27</t>
+          <t>E67</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Page 2 - Portfolio</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2574,30 +2940,30 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>bullet_0</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>E27</t>
+          <t>A68</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Page 2 - Portfolio</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -2606,30 +2972,30 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>bullet_0</t>
+          <t>bullet_1</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>A28</t>
+          <t>A70</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Page 2 - Portfolio</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -2638,16 +3004,2082 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>bullet_1</t>
+          <t>bullet_2</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
+          <t>A72</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Resume</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" t="n">
+        <v>3</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>block_heading</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>A76</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Resume</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" t="n">
+        <v>3</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>list_item</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>A77</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Resume</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" t="n">
+        <v>4</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>block_heading</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>A80</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Resume</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" t="n">
+        <v>4</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>list_item</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>A81</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Resume</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>0</v>
+      </c>
+      <c r="C63" t="n">
+        <v>4</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>list_item</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>A83</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Resume</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" t="n">
+        <v>4</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>list_item</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>2</v>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>A85</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Resume</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" t="n">
+        <v>4</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>list_item</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>3</v>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>A87</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Resume</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" t="n">
+        <v>5</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>block_heading</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>A90</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Resume</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" t="n">
+        <v>5</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>list_item</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>A91</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Resume</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>0</v>
+      </c>
+      <c r="C68" t="n">
+        <v>5</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>list_item</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>A93</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Resume</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" t="n">
+        <v>5</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>list_item</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>2</v>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>A95</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Resume</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" t="n">
+        <v>6</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>block_heading</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>A98</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Resume</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" t="n">
+        <v>6</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>list_item</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>A99</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>1</v>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>headline</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>1</v>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>contact</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>1</v>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>page_title</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>1</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>block_heading</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>A7</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>1</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>1</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>dates</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>E8</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>1</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>organization</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>A9</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>1</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>E9</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>1</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>bullet_0</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>A10</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>bullet_1</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>A12</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>1</v>
+      </c>
+      <c r="C83" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>A15</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>1</v>
+      </c>
+      <c r="C84" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>dates</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>E15</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>organization</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>A16</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>1</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>E16</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>1</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>bullet_0</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>A17</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>1</v>
+      </c>
+      <c r="C88" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>bullet_1</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>A19</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>1</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>2</v>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>A22</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>1</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>dates</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>2</v>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>E22</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>1</v>
+      </c>
+      <c r="C91" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>organization</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>2</v>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>A23</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>1</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>2</v>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>E23</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>1</v>
+      </c>
+      <c r="C93" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>bullet_0</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>2</v>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>A24</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>1</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>bullet_1</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>2</v>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>A26</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>3</v>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>A29</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>dates</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>3</v>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>E29</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>1</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>organization</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>3</v>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
+        <is>
           <t>A30</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>1</v>
+      </c>
+      <c r="C98" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>3</v>
+      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>E30</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>1</v>
+      </c>
+      <c r="C99" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>bullet_0</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>3</v>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>A31</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>1</v>
+      </c>
+      <c r="C100" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>bullet_1</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>3</v>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>A33</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>1</v>
+      </c>
+      <c r="C101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>4</v>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>A36</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>dates</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>4</v>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>E36</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>1</v>
+      </c>
+      <c r="C103" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>organization</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>4</v>
+      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>A37</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>1</v>
+      </c>
+      <c r="C104" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>4</v>
+      </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>E37</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>1</v>
+      </c>
+      <c r="C105" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>bullet_0</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>4</v>
+      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>A38</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>1</v>
+      </c>
+      <c r="C106" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>bullet_1</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>4</v>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>A40</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>1</v>
+      </c>
+      <c r="C107" t="n">
+        <v>1</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>block_heading</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>A44</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>1</v>
+      </c>
+      <c r="C108" t="n">
+        <v>1</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>A45</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>1</v>
+      </c>
+      <c r="C109" t="n">
+        <v>1</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>dates</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>E45</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>1</v>
+      </c>
+      <c r="C110" t="n">
+        <v>1</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>organization</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>A46</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>1</v>
+      </c>
+      <c r="C111" t="n">
+        <v>1</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>E46</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>1</v>
+      </c>
+      <c r="C112" t="n">
+        <v>1</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>bullet_0</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>A47</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>1</v>
+      </c>
+      <c r="C113" t="n">
+        <v>1</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>bullet_1</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>A49</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>1</v>
+      </c>
+      <c r="C114" t="n">
+        <v>2</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>block_heading</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>A53</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>1</v>
+      </c>
+      <c r="C115" t="n">
+        <v>2</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>A54</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>1</v>
+      </c>
+      <c r="C116" t="n">
+        <v>2</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>dates</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>E54</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>1</v>
+      </c>
+      <c r="C117" t="n">
+        <v>2</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>organization</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>A55</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>1</v>
+      </c>
+      <c r="C118" t="n">
+        <v>2</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>E55</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>1</v>
+      </c>
+      <c r="C119" t="n">
+        <v>2</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>bullet_0</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>A56</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>1</v>
+      </c>
+      <c r="C120" t="n">
+        <v>2</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>1</v>
+      </c>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>A59</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>1</v>
+      </c>
+      <c r="C121" t="n">
+        <v>2</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>dates</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>1</v>
+      </c>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>E59</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>1</v>
+      </c>
+      <c r="C122" t="n">
+        <v>2</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>organization</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>1</v>
+      </c>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>A60</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>1</v>
+      </c>
+      <c r="C123" t="n">
+        <v>2</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>E60</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>1</v>
+      </c>
+      <c r="C124" t="n">
+        <v>2</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>section</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>bullet_0</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>1</v>
+      </c>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>A61</t>
         </is>
       </c>
     </row>
@@ -2762,7 +5194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2792,7 +5224,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>[Insert degree, discipline, or target role]</t>
+          <t>I am dedicated to continuous learning and excited to contribute innovative solutions to a company that shares my values of sustainability, responsibility, and respect.</t>
         </is>
       </c>
       <c r="B2" s="5" t="n"/>
@@ -2806,7 +5238,7 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>[insert email] | [insert phone] | [insert city, province] | [insert LinkedIn] | [insert GitHub or portfolio URL]</t>
+          <t>219 Parkside Cress, SE | Calgary, AB, T2J4J3 | (403) 826-9320 | conradashwin@gmail.com | ashwinconrad.ca</t>
         </is>
       </c>
       <c r="B3" s="5" t="n"/>
@@ -2821,7 +5253,7 @@
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Work Experience, Skills &amp; Volunteering</t>
+          <t>Resume</t>
         </is>
       </c>
       <c r="B5" s="6" t="n"/>
@@ -2836,7 +5268,7 @@
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Work Experience</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -2850,7 +5282,7 @@
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>[insert job title]</t>
+          <t>Mechanical Engineering</t>
         </is>
       </c>
       <c r="B8" s="8" t="n"/>
@@ -2858,7 +5290,7 @@
       <c r="D8" s="8" t="n"/>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>[insert dates]</t>
+          <t>2023 - Present</t>
         </is>
       </c>
       <c r="F8" s="9" t="n"/>
@@ -2868,7 +5300,7 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>[insert company]</t>
+          <t>University of Alberta</t>
         </is>
       </c>
       <c r="B9" s="10" t="n"/>
@@ -2876,7 +5308,7 @@
       <c r="D9" s="10" t="n"/>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>[insert location]</t>
+          <t>Edmonton, AB</t>
         </is>
       </c>
       <c r="F9" s="9" t="n"/>
@@ -2886,7 +5318,7 @@
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>[insert impact-focused bullet with action, technical detail, and result]</t>
+          <t>2nd Year Engineering Student</t>
         </is>
       </c>
       <c r="B10" s="10" t="n"/>
@@ -2910,7 +5342,7 @@
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>[insert second bullet focused on tools, process, or collaboration]</t>
+          <t>Extra Curricular: Engineering Student Engagement Leader, Society of Automotive Engineers Formula Racing Club Member</t>
         </is>
       </c>
       <c r="B12" s="10" t="n"/>
@@ -2931,121 +5363,114 @@
       <c r="G13" s="10" t="n"/>
       <c r="H13" s="10" t="n"/>
     </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>[insert third bullet if needed]</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="n"/>
-      <c r="C14" s="10" t="n"/>
-      <c r="D14" s="10" t="n"/>
-      <c r="E14" s="10" t="n"/>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="10" t="n"/>
-      <c r="H14" s="10" t="n"/>
-    </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="10" t="n"/>
-      <c r="B15" s="10" t="n"/>
-      <c r="C15" s="10" t="n"/>
-      <c r="D15" s="10" t="n"/>
-      <c r="E15" s="10" t="n"/>
-      <c r="F15" s="10" t="n"/>
-      <c r="G15" s="10" t="n"/>
-      <c r="H15" s="10" t="n"/>
-    </row>
-    <row r="16" ht="20" customHeight="1"/>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>[insert job title]</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="n"/>
-      <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="n"/>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t>[insert dates]</t>
-        </is>
-      </c>
-      <c r="F17" s="9" t="n"/>
-      <c r="G17" s="9" t="n"/>
-      <c r="H17" s="9" t="n"/>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>[insert company]</t>
-        </is>
-      </c>
+    <row r="14" ht="20" customHeight="1"/>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Highschool Diploma</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>2020 - 2023</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="9" t="n"/>
+      <c r="H15" s="9" t="n"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>West Island College</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="10" t="n"/>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>Calgary, AB</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="n"/>
+      <c r="G16" s="9" t="n"/>
+      <c r="H16" s="9" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Extra Curricular: LADS Clubs (Male Leadership in the Local Community), Diversity Inclusion Pluralism Committee, Senior Varsity Basketball and Rugby</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="10" t="n"/>
+      <c r="F17" s="10" t="n"/>
+      <c r="G17" s="10" t="n"/>
+      <c r="H17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="10" t="n"/>
       <c r="B18" s="10" t="n"/>
       <c r="C18" s="10" t="n"/>
       <c r="D18" s="10" t="n"/>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>[insert location]</t>
-        </is>
-      </c>
-      <c r="F18" s="9" t="n"/>
-      <c r="G18" s="9" t="n"/>
-      <c r="H18" s="9" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>[insert impact-focused bullet]</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="n"/>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="10" t="n"/>
-      <c r="E19" s="10" t="n"/>
-      <c r="F19" s="10" t="n"/>
-      <c r="G19" s="10" t="n"/>
-      <c r="H19" s="10" t="n"/>
-    </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="10" t="n"/>
-      <c r="B20" s="10" t="n"/>
-      <c r="C20" s="10" t="n"/>
-      <c r="D20" s="10" t="n"/>
-      <c r="E20" s="10" t="n"/>
-      <c r="F20" s="10" t="n"/>
-      <c r="G20" s="10" t="n"/>
-      <c r="H20" s="10" t="n"/>
-    </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>[insert technical or leadership bullet]</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="n"/>
-      <c r="C21" s="10" t="n"/>
-      <c r="D21" s="10" t="n"/>
-      <c r="E21" s="10" t="n"/>
-      <c r="F21" s="10" t="n"/>
-      <c r="G21" s="10" t="n"/>
-      <c r="H21" s="10" t="n"/>
+      <c r="E18" s="10" t="n"/>
+      <c r="F18" s="10" t="n"/>
+      <c r="G18" s="10" t="n"/>
+      <c r="H18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="20" customHeight="1"/>
+    <row r="20" ht="20" customHeight="1"/>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Technical Skills</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="7" t="n"/>
+      <c r="G21" s="7" t="n"/>
+      <c r="H21" s="7" t="n"/>
     </row>
     <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="10" t="n"/>
-      <c r="B22" s="10" t="n"/>
-      <c r="C22" s="10" t="n"/>
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Tools &amp; Technical</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Office 365, AutoCAD &amp; 2D laser cutting, Excel data and statistical analysis, LoggerPro, 3D-modeling &amp; printing, Python, Java</t>
+        </is>
+      </c>
       <c r="D22" s="10" t="n"/>
       <c r="E22" s="10" t="n"/>
       <c r="F22" s="10" t="n"/>
       <c r="G22" s="10" t="n"/>
       <c r="H22" s="10" t="n"/>
     </row>
-    <row r="23" ht="20" customHeight="1"/>
+    <row r="23" ht="24" customHeight="1">
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="10" t="n"/>
+      <c r="F23" s="10" t="n"/>
+      <c r="G23" s="10" t="n"/>
+      <c r="H23" s="10" t="n"/>
+    </row>
     <row r="24" ht="20" customHeight="1"/>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>Skills</t>
+          <t>Experience</t>
         </is>
       </c>
       <c r="B25" s="7" t="n"/>
@@ -3056,44 +5481,50 @@
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="7" t="n"/>
     </row>
-    <row r="26" ht="24" customHeight="1">
+    <row r="26" ht="20" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Mechanical</t>
+          <t>Low Voltage Electronics Lead</t>
         </is>
       </c>
       <c r="B26" s="8" t="n"/>
-      <c r="C26" s="10" t="inlineStr">
-        <is>
-          <t>[insert CAD tool], [insert design skill], [insert manufacturing skill]</t>
-        </is>
-      </c>
-      <c r="D26" s="10" t="n"/>
-      <c r="E26" s="10" t="n"/>
-      <c r="F26" s="10" t="n"/>
-      <c r="G26" s="10" t="n"/>
-      <c r="H26" s="10" t="n"/>
-    </row>
-    <row r="27" ht="24" customHeight="1">
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="8" t="n"/>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>Winter 2025 - Present</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="n"/>
+      <c r="G26" s="9" t="n"/>
+      <c r="H26" s="9" t="n"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>Formula EV Racing</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="n"/>
       <c r="C27" s="10" t="n"/>
       <c r="D27" s="10" t="n"/>
-      <c r="E27" s="10" t="n"/>
-      <c r="F27" s="10" t="n"/>
-      <c r="G27" s="10" t="n"/>
-      <c r="H27" s="10" t="n"/>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>University of Calgary</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="n"/>
+      <c r="G27" s="9" t="n"/>
+      <c r="H27" s="9" t="n"/>
     </row>
     <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>Electrical / Controls</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="n"/>
-      <c r="C28" s="10" t="inlineStr">
-        <is>
-          <t>[insert electronics skill], [insert controls skill], [insert test equipment]</t>
-        </is>
-      </c>
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Lead low-voltage electrical system planning and integration for Formula UA27, coordinating board-level hardware, safety interfaces, and vehicle packaging with the broader team.</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
       <c r="D28" s="10" t="n"/>
       <c r="E28" s="10" t="n"/>
       <c r="F28" s="10" t="n"/>
@@ -3101,6 +5532,8 @@
       <c r="H28" s="10" t="n"/>
     </row>
     <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="10" t="n"/>
+      <c r="B29" s="10" t="n"/>
       <c r="C29" s="10" t="n"/>
       <c r="D29" s="10" t="n"/>
       <c r="E29" s="10" t="n"/>
@@ -3108,111 +5541,108 @@
       <c r="G29" s="10" t="n"/>
       <c r="H29" s="10" t="n"/>
     </row>
-    <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>Software / Data</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="n"/>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>Python, [insert analysis tool], [insert automation or web skill]</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="n"/>
-      <c r="E30" s="10" t="n"/>
-      <c r="F30" s="10" t="n"/>
-      <c r="G30" s="10" t="n"/>
-      <c r="H30" s="10" t="n"/>
-    </row>
-    <row r="31" ht="24" customHeight="1">
-      <c r="C31" s="10" t="n"/>
-      <c r="D31" s="10" t="n"/>
-      <c r="E31" s="10" t="n"/>
-      <c r="F31" s="10" t="n"/>
-      <c r="G31" s="10" t="n"/>
-      <c r="H31" s="10" t="n"/>
-    </row>
-    <row r="32" ht="20" customHeight="1"/>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>Volunteering &amp; Leadership</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="n"/>
-      <c r="C33" s="7" t="n"/>
-      <c r="D33" s="7" t="n"/>
-      <c r="E33" s="7" t="n"/>
-      <c r="F33" s="7" t="n"/>
-      <c r="G33" s="7" t="n"/>
-      <c r="H33" s="7" t="n"/>
-    </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>[insert volunteer or leadership role]</t>
-        </is>
-      </c>
-      <c r="B34" s="8" t="n"/>
-      <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="n"/>
-      <c r="E34" s="9" t="inlineStr">
-        <is>
-          <t>[insert dates]</t>
-        </is>
-      </c>
-      <c r="F34" s="9" t="n"/>
-      <c r="G34" s="9" t="n"/>
-      <c r="H34" s="9" t="n"/>
-    </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="10" t="inlineStr">
-        <is>
-          <t>[insert organization]</t>
-        </is>
-      </c>
-      <c r="B35" s="10" t="n"/>
-      <c r="C35" s="10" t="n"/>
-      <c r="D35" s="10" t="n"/>
-      <c r="E35" s="9" t="inlineStr">
-        <is>
-          <t>[insert location]</t>
-        </is>
-      </c>
-      <c r="F35" s="9" t="n"/>
-      <c r="G35" s="9" t="n"/>
-      <c r="H35" s="9" t="n"/>
-    </row>
-    <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t>[insert leadership, mentoring, fundraising, event, or service contribution]</t>
-        </is>
-      </c>
-      <c r="B36" s="10" t="n"/>
-      <c r="C36" s="10" t="n"/>
-      <c r="D36" s="10" t="n"/>
-      <c r="E36" s="10" t="n"/>
-      <c r="F36" s="10" t="n"/>
-      <c r="G36" s="10" t="n"/>
-      <c r="H36" s="10" t="n"/>
-    </row>
-    <row r="37" ht="24" customHeight="1">
-      <c r="A37" s="10" t="n"/>
+    <row r="30" ht="20" customHeight="1"/>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Engineering Co-op</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="n"/>
+      <c r="C31" s="8" t="n"/>
+      <c r="D31" s="8" t="n"/>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>2025 - 2026</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="n"/>
+      <c r="G31" s="9" t="n"/>
+      <c r="H31" s="9" t="n"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>AltaGas</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>Calgary, AB</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="n"/>
+      <c r="G32" s="9" t="n"/>
+      <c r="H32" s="9" t="n"/>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>Built automation and data-analysis workflows for corrosion monitoring, inspection planning, and asset lifecycle work across multi-facility operations.</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="10" t="n"/>
+      <c r="G33" s="10" t="n"/>
+      <c r="H33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="10" t="n"/>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="10" t="n"/>
+      <c r="G34" s="10" t="n"/>
+      <c r="H34" s="10" t="n"/>
+    </row>
+    <row r="35" ht="20" customHeight="1"/>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>Control Panel Technician</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="n"/>
+      <c r="C36" s="8" t="n"/>
+      <c r="D36" s="8" t="n"/>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>Summer Terms, '23, '24</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="n"/>
+      <c r="G36" s="9" t="n"/>
+      <c r="H36" s="9" t="n"/>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>Spartan Controls</t>
+        </is>
+      </c>
       <c r="B37" s="10" t="n"/>
       <c r="C37" s="10" t="n"/>
       <c r="D37" s="10" t="n"/>
-      <c r="E37" s="10" t="n"/>
-      <c r="F37" s="10" t="n"/>
-      <c r="G37" s="10" t="n"/>
-      <c r="H37" s="10" t="n"/>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>Calgary, AB</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="n"/>
+      <c r="G37" s="9" t="n"/>
+      <c r="H37" s="9" t="n"/>
     </row>
     <row r="38" ht="24" customHeight="1">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>[insert measurable outcome or responsibility]</t>
+          <t>Gained hands-on experience in remote transmission units, RTU, and electrical departments, focusing on panel production and quality assurance.</t>
         </is>
       </c>
       <c r="B38" s="10" t="n"/>
@@ -3233,43 +5663,767 @@
       <c r="G39" s="10" t="n"/>
       <c r="H39" s="10" t="n"/>
     </row>
-    <row r="40" ht="20" customHeight="1"/>
-    <row r="41" ht="20" customHeight="1"/>
-    <row r="42" ht="20" customHeight="1"/>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>Completed 15+ multi-panel projects in individual, partner-based, and group setups, consistently meeting and exceeding expectations.</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="10" t="n"/>
+      <c r="G40" s="10" t="n"/>
+      <c r="H40" s="10" t="n"/>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="10" t="n"/>
+      <c r="B41" s="10" t="n"/>
+      <c r="C41" s="10" t="n"/>
+      <c r="D41" s="10" t="n"/>
+      <c r="E41" s="10" t="n"/>
+      <c r="F41" s="10" t="n"/>
+      <c r="G41" s="10" t="n"/>
+      <c r="H41" s="10" t="n"/>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>Interpreted and analyzed engineering drawings, panel designs, and electrical schematics.</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="n"/>
+      <c r="C42" s="10" t="n"/>
+      <c r="D42" s="10" t="n"/>
+      <c r="E42" s="10" t="n"/>
+      <c r="F42" s="10" t="n"/>
+      <c r="G42" s="10" t="n"/>
+      <c r="H42" s="10" t="n"/>
+    </row>
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" s="10" t="n"/>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="10" t="n"/>
+      <c r="D43" s="10" t="n"/>
+      <c r="E43" s="10" t="n"/>
+      <c r="F43" s="10" t="n"/>
+      <c r="G43" s="10" t="n"/>
+      <c r="H43" s="10" t="n"/>
+    </row>
+    <row r="44" ht="24" customHeight="1">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>Worked extensively with advanced panel systems, including various industry-standard Distributed Control Systems, DCS, and signal transmission and power supply units.</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="n"/>
+      <c r="C44" s="10" t="n"/>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="10" t="n"/>
+      <c r="F44" s="10" t="n"/>
+      <c r="G44" s="10" t="n"/>
+      <c r="H44" s="10" t="n"/>
+    </row>
+    <row r="45" ht="24" customHeight="1">
+      <c r="A45" s="10" t="n"/>
+      <c r="B45" s="10" t="n"/>
+      <c r="C45" s="10" t="n"/>
+      <c r="D45" s="10" t="n"/>
+      <c r="E45" s="10" t="n"/>
+      <c r="F45" s="10" t="n"/>
+      <c r="G45" s="10" t="n"/>
+      <c r="H45" s="10" t="n"/>
+    </row>
+    <row r="46" ht="24" customHeight="1">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>Resolved quality control issues accurately and met strict deadlines.</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="n"/>
+      <c r="C46" s="10" t="n"/>
+      <c r="D46" s="10" t="n"/>
+      <c r="E46" s="10" t="n"/>
+      <c r="F46" s="10" t="n"/>
+      <c r="G46" s="10" t="n"/>
+      <c r="H46" s="10" t="n"/>
+    </row>
+    <row r="47" ht="24" customHeight="1">
+      <c r="A47" s="10" t="n"/>
+      <c r="B47" s="10" t="n"/>
+      <c r="C47" s="10" t="n"/>
+      <c r="D47" s="10" t="n"/>
+      <c r="E47" s="10" t="n"/>
+      <c r="F47" s="10" t="n"/>
+      <c r="G47" s="10" t="n"/>
+      <c r="H47" s="10" t="n"/>
+    </row>
+    <row r="48" ht="24" customHeight="1">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>Assisted with pressure and instrumentation testing for RemVue Control Panels and processed 250+ PLC software updates in under half the allocated time.</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="n"/>
+      <c r="C48" s="10" t="n"/>
+      <c r="D48" s="10" t="n"/>
+      <c r="E48" s="10" t="n"/>
+      <c r="F48" s="10" t="n"/>
+      <c r="G48" s="10" t="n"/>
+      <c r="H48" s="10" t="n"/>
+    </row>
+    <row r="49" ht="24" customHeight="1">
+      <c r="A49" s="10" t="n"/>
+      <c r="B49" s="10" t="n"/>
+      <c r="C49" s="10" t="n"/>
+      <c r="D49" s="10" t="n"/>
+      <c r="E49" s="10" t="n"/>
+      <c r="F49" s="10" t="n"/>
+      <c r="G49" s="10" t="n"/>
+      <c r="H49" s="10" t="n"/>
+    </row>
+    <row r="50" ht="24" customHeight="1">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>Collaborated in team environments emphasizing safety and efficiency.</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="n"/>
+      <c r="C50" s="10" t="n"/>
+      <c r="D50" s="10" t="n"/>
+      <c r="E50" s="10" t="n"/>
+      <c r="F50" s="10" t="n"/>
+      <c r="G50" s="10" t="n"/>
+      <c r="H50" s="10" t="n"/>
+    </row>
+    <row r="51" ht="24" customHeight="1">
+      <c r="A51" s="10" t="n"/>
+      <c r="B51" s="10" t="n"/>
+      <c r="C51" s="10" t="n"/>
+      <c r="D51" s="10" t="n"/>
+      <c r="E51" s="10" t="n"/>
+      <c r="F51" s="10" t="n"/>
+      <c r="G51" s="10" t="n"/>
+      <c r="H51" s="10" t="n"/>
+    </row>
+    <row r="52" ht="24" customHeight="1">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>Applied technical understanding and precision skills in panel assembly while adhering to high standards and identifying deficiencies.</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="n"/>
+      <c r="C52" s="10" t="n"/>
+      <c r="D52" s="10" t="n"/>
+      <c r="E52" s="10" t="n"/>
+      <c r="F52" s="10" t="n"/>
+      <c r="G52" s="10" t="n"/>
+      <c r="H52" s="10" t="n"/>
+    </row>
+    <row r="53" ht="24" customHeight="1">
+      <c r="A53" s="10" t="n"/>
+      <c r="B53" s="10" t="n"/>
+      <c r="C53" s="10" t="n"/>
+      <c r="D53" s="10" t="n"/>
+      <c r="E53" s="10" t="n"/>
+      <c r="F53" s="10" t="n"/>
+      <c r="G53" s="10" t="n"/>
+      <c r="H53" s="10" t="n"/>
+    </row>
+    <row r="54" ht="20" customHeight="1"/>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>Floor Worker/Cashier</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="n"/>
+      <c r="C55" s="8" t="n"/>
+      <c r="D55" s="8" t="n"/>
+      <c r="E55" s="9" t="inlineStr">
+        <is>
+          <t>Mar 2022 - Jul 2023</t>
+        </is>
+      </c>
+      <c r="F55" s="9" t="n"/>
+      <c r="G55" s="9" t="n"/>
+      <c r="H55" s="9" t="n"/>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>Cherry Pit</t>
+        </is>
+      </c>
+      <c r="B56" s="10" t="n"/>
+      <c r="C56" s="10" t="n"/>
+      <c r="D56" s="10" t="n"/>
+      <c r="E56" s="9" t="inlineStr">
+        <is>
+          <t>Calgary, AB</t>
+        </is>
+      </c>
+      <c r="F56" s="9" t="n"/>
+      <c r="G56" s="9" t="n"/>
+      <c r="H56" s="9" t="n"/>
+    </row>
+    <row r="57" ht="24" customHeight="1">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>Stocked vegetable displays and provided customer service.</t>
+        </is>
+      </c>
+      <c r="B57" s="10" t="n"/>
+      <c r="C57" s="10" t="n"/>
+      <c r="D57" s="10" t="n"/>
+      <c r="E57" s="10" t="n"/>
+      <c r="F57" s="10" t="n"/>
+      <c r="G57" s="10" t="n"/>
+      <c r="H57" s="10" t="n"/>
+    </row>
+    <row r="58" ht="24" customHeight="1">
+      <c r="A58" s="10" t="n"/>
+      <c r="B58" s="10" t="n"/>
+      <c r="C58" s="10" t="n"/>
+      <c r="D58" s="10" t="n"/>
+      <c r="E58" s="10" t="n"/>
+      <c r="F58" s="10" t="n"/>
+      <c r="G58" s="10" t="n"/>
+      <c r="H58" s="10" t="n"/>
+    </row>
+    <row r="59" ht="24" customHeight="1">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>Conducted timely deliveries to customers and businesses.</t>
+        </is>
+      </c>
+      <c r="B59" s="10" t="n"/>
+      <c r="C59" s="10" t="n"/>
+      <c r="D59" s="10" t="n"/>
+      <c r="E59" s="10" t="n"/>
+      <c r="F59" s="10" t="n"/>
+      <c r="G59" s="10" t="n"/>
+      <c r="H59" s="10" t="n"/>
+    </row>
+    <row r="60" ht="24" customHeight="1">
+      <c r="A60" s="10" t="n"/>
+      <c r="B60" s="10" t="n"/>
+      <c r="C60" s="10" t="n"/>
+      <c r="D60" s="10" t="n"/>
+      <c r="E60" s="10" t="n"/>
+      <c r="F60" s="10" t="n"/>
+      <c r="G60" s="10" t="n"/>
+      <c r="H60" s="10" t="n"/>
+    </row>
+    <row r="61" ht="24" customHeight="1">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>Managed and organized incoming pallets.</t>
+        </is>
+      </c>
+      <c r="B61" s="10" t="n"/>
+      <c r="C61" s="10" t="n"/>
+      <c r="D61" s="10" t="n"/>
+      <c r="E61" s="10" t="n"/>
+      <c r="F61" s="10" t="n"/>
+      <c r="G61" s="10" t="n"/>
+      <c r="H61" s="10" t="n"/>
+    </row>
+    <row r="62" ht="24" customHeight="1">
+      <c r="A62" s="10" t="n"/>
+      <c r="B62" s="10" t="n"/>
+      <c r="C62" s="10" t="n"/>
+      <c r="D62" s="10" t="n"/>
+      <c r="E62" s="10" t="n"/>
+      <c r="F62" s="10" t="n"/>
+      <c r="G62" s="10" t="n"/>
+      <c r="H62" s="10" t="n"/>
+    </row>
+    <row r="63" ht="24" customHeight="1">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>Assisted in training new hires.</t>
+        </is>
+      </c>
+      <c r="B63" s="10" t="n"/>
+      <c r="C63" s="10" t="n"/>
+      <c r="D63" s="10" t="n"/>
+      <c r="E63" s="10" t="n"/>
+      <c r="F63" s="10" t="n"/>
+      <c r="G63" s="10" t="n"/>
+      <c r="H63" s="10" t="n"/>
+    </row>
+    <row r="64" ht="24" customHeight="1">
+      <c r="A64" s="10" t="n"/>
+      <c r="B64" s="10" t="n"/>
+      <c r="C64" s="10" t="n"/>
+      <c r="D64" s="10" t="n"/>
+      <c r="E64" s="10" t="n"/>
+      <c r="F64" s="10" t="n"/>
+      <c r="G64" s="10" t="n"/>
+      <c r="H64" s="10" t="n"/>
+    </row>
+    <row r="65" ht="20" customHeight="1"/>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>Service Technician</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="n"/>
+      <c r="C66" s="8" t="n"/>
+      <c r="D66" s="8" t="n"/>
+      <c r="E66" s="9" t="inlineStr">
+        <is>
+          <t>Dec 2019 - Sep 2022</t>
+        </is>
+      </c>
+      <c r="F66" s="9" t="n"/>
+      <c r="G66" s="9" t="n"/>
+      <c r="H66" s="9" t="n"/>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>A-Plus Parking</t>
+        </is>
+      </c>
+      <c r="B67" s="10" t="n"/>
+      <c r="C67" s="10" t="n"/>
+      <c r="D67" s="10" t="n"/>
+      <c r="E67" s="9" t="inlineStr">
+        <is>
+          <t>Calgary, AB</t>
+        </is>
+      </c>
+      <c r="F67" s="9" t="n"/>
+      <c r="G67" s="9" t="n"/>
+      <c r="H67" s="9" t="n"/>
+    </row>
+    <row r="68" ht="24" customHeight="1">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t>Completed general maintenance and troubleshooting repairs on trucks, trailers, and old/broken equipment.</t>
+        </is>
+      </c>
+      <c r="B68" s="10" t="n"/>
+      <c r="C68" s="10" t="n"/>
+      <c r="D68" s="10" t="n"/>
+      <c r="E68" s="10" t="n"/>
+      <c r="F68" s="10" t="n"/>
+      <c r="G68" s="10" t="n"/>
+      <c r="H68" s="10" t="n"/>
+    </row>
+    <row r="69" ht="24" customHeight="1">
+      <c r="A69" s="10" t="n"/>
+      <c r="B69" s="10" t="n"/>
+      <c r="C69" s="10" t="n"/>
+      <c r="D69" s="10" t="n"/>
+      <c r="E69" s="10" t="n"/>
+      <c r="F69" s="10" t="n"/>
+      <c r="G69" s="10" t="n"/>
+      <c r="H69" s="10" t="n"/>
+    </row>
+    <row r="70" ht="24" customHeight="1">
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <t>Silicon moulded and 2 part casted bumper plates for street-sweeping equipment, reducing the cost of single-use products by 50%.</t>
+        </is>
+      </c>
+      <c r="B70" s="10" t="n"/>
+      <c r="C70" s="10" t="n"/>
+      <c r="D70" s="10" t="n"/>
+      <c r="E70" s="10" t="n"/>
+      <c r="F70" s="10" t="n"/>
+      <c r="G70" s="10" t="n"/>
+      <c r="H70" s="10" t="n"/>
+    </row>
+    <row r="71" ht="24" customHeight="1">
+      <c r="A71" s="10" t="n"/>
+      <c r="B71" s="10" t="n"/>
+      <c r="C71" s="10" t="n"/>
+      <c r="D71" s="10" t="n"/>
+      <c r="E71" s="10" t="n"/>
+      <c r="F71" s="10" t="n"/>
+      <c r="G71" s="10" t="n"/>
+      <c r="H71" s="10" t="n"/>
+    </row>
+    <row r="72" ht="24" customHeight="1">
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>Assisted with bookkeeping, painting parkade lines, and cleaning.</t>
+        </is>
+      </c>
+      <c r="B72" s="10" t="n"/>
+      <c r="C72" s="10" t="n"/>
+      <c r="D72" s="10" t="n"/>
+      <c r="E72" s="10" t="n"/>
+      <c r="F72" s="10" t="n"/>
+      <c r="G72" s="10" t="n"/>
+      <c r="H72" s="10" t="n"/>
+    </row>
+    <row r="73" ht="24" customHeight="1">
+      <c r="A73" s="10" t="n"/>
+      <c r="B73" s="10" t="n"/>
+      <c r="C73" s="10" t="n"/>
+      <c r="D73" s="10" t="n"/>
+      <c r="E73" s="10" t="n"/>
+      <c r="F73" s="10" t="n"/>
+      <c r="G73" s="10" t="n"/>
+      <c r="H73" s="10" t="n"/>
+    </row>
+    <row r="74" ht="20" customHeight="1"/>
+    <row r="75" ht="20" customHeight="1"/>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>Skills</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="n"/>
+      <c r="C76" s="7" t="n"/>
+      <c r="D76" s="7" t="n"/>
+      <c r="E76" s="7" t="n"/>
+      <c r="F76" s="7" t="n"/>
+      <c r="G76" s="7" t="n"/>
+      <c r="H76" s="7" t="n"/>
+    </row>
+    <row r="77" ht="24" customHeight="1">
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>Leadership &amp; Teamwork - Organization - Trouble Shooting/Problem Solving - Fast Learner</t>
+        </is>
+      </c>
+      <c r="B77" s="10" t="n"/>
+      <c r="C77" s="10" t="n"/>
+      <c r="D77" s="10" t="n"/>
+      <c r="E77" s="10" t="n"/>
+      <c r="F77" s="10" t="n"/>
+      <c r="G77" s="10" t="n"/>
+      <c r="H77" s="10" t="n"/>
+    </row>
+    <row r="78" ht="24" customHeight="1">
+      <c r="A78" s="10" t="n"/>
+      <c r="B78" s="10" t="n"/>
+      <c r="C78" s="10" t="n"/>
+      <c r="D78" s="10" t="n"/>
+      <c r="E78" s="10" t="n"/>
+      <c r="F78" s="10" t="n"/>
+      <c r="G78" s="10" t="n"/>
+      <c r="H78" s="10" t="n"/>
+    </row>
+    <row r="79" ht="20" customHeight="1"/>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>Awards</t>
+        </is>
+      </c>
+      <c r="B80" s="7" t="n"/>
+      <c r="C80" s="7" t="n"/>
+      <c r="D80" s="7" t="n"/>
+      <c r="E80" s="7" t="n"/>
+      <c r="F80" s="7" t="n"/>
+      <c r="G80" s="7" t="n"/>
+      <c r="H80" s="7" t="n"/>
+    </row>
+    <row r="81" ht="24" customHeight="1">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>Undergraduate Student Leadership Award Winner - 2024-2025</t>
+        </is>
+      </c>
+      <c r="B81" s="10" t="n"/>
+      <c r="C81" s="10" t="n"/>
+      <c r="D81" s="10" t="n"/>
+      <c r="E81" s="10" t="n"/>
+      <c r="F81" s="10" t="n"/>
+      <c r="G81" s="10" t="n"/>
+      <c r="H81" s="10" t="n"/>
+    </row>
+    <row r="82" ht="24" customHeight="1">
+      <c r="A82" s="10" t="n"/>
+      <c r="B82" s="10" t="n"/>
+      <c r="C82" s="10" t="n"/>
+      <c r="D82" s="10" t="n"/>
+      <c r="E82" s="10" t="n"/>
+      <c r="F82" s="10" t="n"/>
+      <c r="G82" s="10" t="n"/>
+      <c r="H82" s="10" t="n"/>
+    </row>
+    <row r="83" ht="24" customHeight="1">
+      <c r="A83" s="10" t="inlineStr">
+        <is>
+          <t>Nomination for Best Project - Eng 160 Final Project 2024</t>
+        </is>
+      </c>
+      <c r="B83" s="10" t="n"/>
+      <c r="C83" s="10" t="n"/>
+      <c r="D83" s="10" t="n"/>
+      <c r="E83" s="10" t="n"/>
+      <c r="F83" s="10" t="n"/>
+      <c r="G83" s="10" t="n"/>
+      <c r="H83" s="10" t="n"/>
+    </row>
+    <row r="84" ht="24" customHeight="1">
+      <c r="A84" s="10" t="n"/>
+      <c r="B84" s="10" t="n"/>
+      <c r="C84" s="10" t="n"/>
+      <c r="D84" s="10" t="n"/>
+      <c r="E84" s="10" t="n"/>
+      <c r="F84" s="10" t="n"/>
+      <c r="G84" s="10" t="n"/>
+      <c r="H84" s="10" t="n"/>
+    </row>
+    <row r="85" ht="24" customHeight="1">
+      <c r="A85" s="10" t="inlineStr">
+        <is>
+          <t>Leadership in Engineering Scholarship Winner 2023-2024</t>
+        </is>
+      </c>
+      <c r="B85" s="10" t="n"/>
+      <c r="C85" s="10" t="n"/>
+      <c r="D85" s="10" t="n"/>
+      <c r="E85" s="10" t="n"/>
+      <c r="F85" s="10" t="n"/>
+      <c r="G85" s="10" t="n"/>
+      <c r="H85" s="10" t="n"/>
+    </row>
+    <row r="86" ht="24" customHeight="1">
+      <c r="A86" s="10" t="n"/>
+      <c r="B86" s="10" t="n"/>
+      <c r="C86" s="10" t="n"/>
+      <c r="D86" s="10" t="n"/>
+      <c r="E86" s="10" t="n"/>
+      <c r="F86" s="10" t="n"/>
+      <c r="G86" s="10" t="n"/>
+      <c r="H86" s="10" t="n"/>
+    </row>
+    <row r="87" ht="24" customHeight="1">
+      <c r="A87" s="10" t="inlineStr">
+        <is>
+          <t>APEGA Science Olympics Medalist: Silver 2021-2022, Silver 2022-2023</t>
+        </is>
+      </c>
+      <c r="B87" s="10" t="n"/>
+      <c r="C87" s="10" t="n"/>
+      <c r="D87" s="10" t="n"/>
+      <c r="E87" s="10" t="n"/>
+      <c r="F87" s="10" t="n"/>
+      <c r="G87" s="10" t="n"/>
+      <c r="H87" s="10" t="n"/>
+    </row>
+    <row r="88" ht="24" customHeight="1">
+      <c r="A88" s="10" t="n"/>
+      <c r="B88" s="10" t="n"/>
+      <c r="C88" s="10" t="n"/>
+      <c r="D88" s="10" t="n"/>
+      <c r="E88" s="10" t="n"/>
+      <c r="F88" s="10" t="n"/>
+      <c r="G88" s="10" t="n"/>
+      <c r="H88" s="10" t="n"/>
+    </row>
+    <row r="89" ht="20" customHeight="1"/>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>Volunteering</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="n"/>
+      <c r="C90" s="7" t="n"/>
+      <c r="D90" s="7" t="n"/>
+      <c r="E90" s="7" t="n"/>
+      <c r="F90" s="7" t="n"/>
+      <c r="G90" s="7" t="n"/>
+      <c r="H90" s="7" t="n"/>
+    </row>
+    <row r="91" ht="24" customHeight="1">
+      <c r="A91" s="10" t="inlineStr">
+        <is>
+          <t>Engineering Student Engagement Leader 2024-2025</t>
+        </is>
+      </c>
+      <c r="B91" s="10" t="n"/>
+      <c r="C91" s="10" t="n"/>
+      <c r="D91" s="10" t="n"/>
+      <c r="E91" s="10" t="n"/>
+      <c r="F91" s="10" t="n"/>
+      <c r="G91" s="10" t="n"/>
+      <c r="H91" s="10" t="n"/>
+    </row>
+    <row r="92" ht="24" customHeight="1">
+      <c r="A92" s="10" t="n"/>
+      <c r="B92" s="10" t="n"/>
+      <c r="C92" s="10" t="n"/>
+      <c r="D92" s="10" t="n"/>
+      <c r="E92" s="10" t="n"/>
+      <c r="F92" s="10" t="n"/>
+      <c r="G92" s="10" t="n"/>
+      <c r="H92" s="10" t="n"/>
+    </row>
+    <row r="93" ht="24" customHeight="1">
+      <c r="A93" s="10" t="inlineStr">
+        <is>
+          <t>CYDC Assistant Youth Basketball Coach 2024</t>
+        </is>
+      </c>
+      <c r="B93" s="10" t="n"/>
+      <c r="C93" s="10" t="n"/>
+      <c r="D93" s="10" t="n"/>
+      <c r="E93" s="10" t="n"/>
+      <c r="F93" s="10" t="n"/>
+      <c r="G93" s="10" t="n"/>
+      <c r="H93" s="10" t="n"/>
+    </row>
+    <row r="94" ht="24" customHeight="1">
+      <c r="A94" s="10" t="n"/>
+      <c r="B94" s="10" t="n"/>
+      <c r="C94" s="10" t="n"/>
+      <c r="D94" s="10" t="n"/>
+      <c r="E94" s="10" t="n"/>
+      <c r="F94" s="10" t="n"/>
+      <c r="G94" s="10" t="n"/>
+      <c r="H94" s="10" t="n"/>
+    </row>
+    <row r="95" ht="24" customHeight="1">
+      <c r="A95" s="10" t="inlineStr">
+        <is>
+          <t>WIC Grade 7-8 Head &amp; Assistant Basketball Coach 2022-2023</t>
+        </is>
+      </c>
+      <c r="B95" s="10" t="n"/>
+      <c r="C95" s="10" t="n"/>
+      <c r="D95" s="10" t="n"/>
+      <c r="E95" s="10" t="n"/>
+      <c r="F95" s="10" t="n"/>
+      <c r="G95" s="10" t="n"/>
+      <c r="H95" s="10" t="n"/>
+    </row>
+    <row r="96" ht="24" customHeight="1">
+      <c r="A96" s="10" t="n"/>
+      <c r="B96" s="10" t="n"/>
+      <c r="C96" s="10" t="n"/>
+      <c r="D96" s="10" t="n"/>
+      <c r="E96" s="10" t="n"/>
+      <c r="F96" s="10" t="n"/>
+      <c r="G96" s="10" t="n"/>
+      <c r="H96" s="10" t="n"/>
+    </row>
+    <row r="97" ht="20" customHeight="1"/>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="7" t="inlineStr">
+        <is>
+          <t>Personal Interests</t>
+        </is>
+      </c>
+      <c r="B98" s="7" t="n"/>
+      <c r="C98" s="7" t="n"/>
+      <c r="D98" s="7" t="n"/>
+      <c r="E98" s="7" t="n"/>
+      <c r="F98" s="7" t="n"/>
+      <c r="G98" s="7" t="n"/>
+      <c r="H98" s="7" t="n"/>
+    </row>
+    <row r="99" ht="24" customHeight="1">
+      <c r="A99" s="10" t="inlineStr">
+        <is>
+          <t>Cooking - Physical Fitness - metal/wood/leather/composite material design and projects</t>
+        </is>
+      </c>
+      <c r="B99" s="10" t="n"/>
+      <c r="C99" s="10" t="n"/>
+      <c r="D99" s="10" t="n"/>
+      <c r="E99" s="10" t="n"/>
+      <c r="F99" s="10" t="n"/>
+      <c r="G99" s="10" t="n"/>
+      <c r="H99" s="10" t="n"/>
+    </row>
+    <row r="100" ht="24" customHeight="1">
+      <c r="A100" s="10" t="n"/>
+      <c r="B100" s="10" t="n"/>
+      <c r="C100" s="10" t="n"/>
+      <c r="D100" s="10" t="n"/>
+      <c r="E100" s="10" t="n"/>
+      <c r="F100" s="10" t="n"/>
+      <c r="G100" s="10" t="n"/>
+      <c r="H100" s="10" t="n"/>
+    </row>
+    <row r="101" ht="20" customHeight="1"/>
+    <row r="102" ht="20" customHeight="1"/>
   </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="A17:D17"/>
+  <mergeCells count="70">
     <mergeCell ref="A12:H13"/>
-    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="E26:H26"/>
     <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A99:H100"/>
+    <mergeCell ref="A46:H47"/>
+    <mergeCell ref="A95:H96"/>
+    <mergeCell ref="A91:H92"/>
+    <mergeCell ref="E16:H16"/>
+    <mergeCell ref="A85:H86"/>
+    <mergeCell ref="A98:H98"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A14:H15"/>
-    <mergeCell ref="A21:H22"/>
-    <mergeCell ref="C28:H29"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="A57:H58"/>
+    <mergeCell ref="E66:H66"/>
+    <mergeCell ref="A17:H18"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="E18:H18"/>
+    <mergeCell ref="A42:H43"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="E56:H56"/>
+    <mergeCell ref="A33:H34"/>
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="A25:H25"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="C30:H31"/>
+    <mergeCell ref="A67:D67"/>
+    <mergeCell ref="A81:H82"/>
+    <mergeCell ref="A77:H78"/>
+    <mergeCell ref="A63:H64"/>
+    <mergeCell ref="A15:D15"/>
     <mergeCell ref="A10:H11"/>
-    <mergeCell ref="A19:H20"/>
+    <mergeCell ref="A72:H73"/>
+    <mergeCell ref="A90:H90"/>
+    <mergeCell ref="A68:H69"/>
+    <mergeCell ref="A80:H80"/>
+    <mergeCell ref="A44:H45"/>
+    <mergeCell ref="E55:H55"/>
+    <mergeCell ref="E67:H67"/>
+    <mergeCell ref="A93:H94"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A38:H39"/>
-    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A52:H53"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="E17:H17"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A28:H29"/>
     <mergeCell ref="E8:H8"/>
-    <mergeCell ref="C26:H27"/>
+    <mergeCell ref="A83:H84"/>
+    <mergeCell ref="A59:H60"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="E35:H35"/>
-    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A87:H88"/>
+    <mergeCell ref="C22:H23"/>
+    <mergeCell ref="A76:H76"/>
+    <mergeCell ref="A40:H41"/>
+    <mergeCell ref="A16:D16"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A48:H49"/>
+    <mergeCell ref="A61:H62"/>
+    <mergeCell ref="A66:D66"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="A56:D56"/>
+    <mergeCell ref="A27:D27"/>
     <mergeCell ref="E9:H9"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="A36:H37"/>
-    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A70:H71"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="A50:H51"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="E36:H36"/>
   </mergeCells>
   <pageMargins left="0.35" right="0.35" top="0.35" bottom="0.35" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="1" fitToHeight="1" fitToWidth="1"/>
@@ -3283,7 +6437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3313,7 +6467,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>[Insert degree, discipline, or target role]</t>
+          <t>I am dedicated to continuous learning and excited to contribute innovative solutions to a company that shares my values of sustainability, responsibility, and respect.</t>
         </is>
       </c>
       <c r="B2" s="5" t="n"/>
@@ -3327,7 +6481,7 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>[insert email] | [insert phone] | [insert city, province] | [insert LinkedIn] | [insert GitHub or portfolio URL]</t>
+          <t>219 Parkside Cress, SE | Calgary, AB, T2J4J3 | (403) 826-9320 | conradashwin@gmail.com | ashwinconrad.ca</t>
         </is>
       </c>
       <c r="B3" s="5" t="n"/>
@@ -3371,7 +6525,7 @@
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>[insert project name]</t>
+          <t>Corrosion Monitoring Dashboard</t>
         </is>
       </c>
       <c r="B8" s="8" t="n"/>
@@ -3379,7 +6533,7 @@
       <c r="D8" s="8" t="n"/>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>[insert dates]</t>
+          <t>2025 - 2026</t>
         </is>
       </c>
       <c r="F8" s="9" t="n"/>
@@ -3389,7 +6543,7 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>[insert course, club, or personal context]</t>
+          <t>AltaGas</t>
         </is>
       </c>
       <c r="B9" s="10" t="n"/>
@@ -3397,7 +6551,7 @@
       <c r="D9" s="10" t="n"/>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>[insert tools or system type]</t>
+          <t>Microsoft Fabric, Power BI, Python</t>
         </is>
       </c>
       <c r="F9" s="9" t="n"/>
@@ -3407,7 +6561,7 @@
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>[insert problem statement and your role]</t>
+          <t>Built a centralized data workflow for corrosion coupon tracking across 12 facilities and 100+ monitored assets.</t>
         </is>
       </c>
       <c r="B10" s="10" t="n"/>
@@ -3431,7 +6585,7 @@
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>[insert design/build/test methods]</t>
+          <t>Reduced manual vendor-report processing by structuring incoming data for repeatable Power BI reporting and analysis.</t>
         </is>
       </c>
       <c r="B12" s="10" t="n"/>
@@ -3452,71 +6606,71 @@
       <c r="G13" s="10" t="n"/>
       <c r="H13" s="10" t="n"/>
     </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>[insert outcome, metric, or lesson learned]</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="n"/>
-      <c r="C14" s="10" t="n"/>
-      <c r="D14" s="10" t="n"/>
-      <c r="E14" s="10" t="n"/>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="10" t="n"/>
-      <c r="H14" s="10" t="n"/>
-    </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="10" t="n"/>
-      <c r="B15" s="10" t="n"/>
-      <c r="C15" s="10" t="n"/>
-      <c r="D15" s="10" t="n"/>
-      <c r="E15" s="10" t="n"/>
-      <c r="F15" s="10" t="n"/>
-      <c r="G15" s="10" t="n"/>
-      <c r="H15" s="10" t="n"/>
-    </row>
-    <row r="16" ht="20" customHeight="1"/>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>[insert project name]</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="n"/>
-      <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="n"/>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t>[insert dates]</t>
-        </is>
-      </c>
-      <c r="F17" s="9" t="n"/>
-      <c r="G17" s="9" t="n"/>
-      <c r="H17" s="9" t="n"/>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>[insert course, club, or personal context]</t>
-        </is>
-      </c>
+    <row r="14" ht="20" customHeight="1"/>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Inspection Scope Generation Tool</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>2025 - 2026</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="9" t="n"/>
+      <c r="H15" s="9" t="n"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>AltaGas</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="10" t="n"/>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>Python, openpyxl, python-docx</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="n"/>
+      <c r="G16" s="9" t="n"/>
+      <c r="H16" s="9" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Developed a Python tool to generate 500+ equipment-specific inspection scopes from database exports.</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="10" t="n"/>
+      <c r="F17" s="10" t="n"/>
+      <c r="G17" s="10" t="n"/>
+      <c r="H17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="10" t="n"/>
       <c r="B18" s="10" t="n"/>
       <c r="C18" s="10" t="n"/>
       <c r="D18" s="10" t="n"/>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>[insert tools or system type]</t>
-        </is>
-      </c>
-      <c r="F18" s="9" t="n"/>
-      <c r="G18" s="9" t="n"/>
-      <c r="H18" s="9" t="n"/>
+      <c r="E18" s="10" t="n"/>
+      <c r="F18" s="10" t="n"/>
+      <c r="G18" s="10" t="n"/>
+      <c r="H18" s="10" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>[insert concise project contribution]</t>
+          <t>Reduced manual document creation time by standardizing Excel-to-Word scope generation.</t>
         </is>
       </c>
       <c r="B19" s="10" t="n"/>
@@ -3537,122 +6691,134 @@
       <c r="G20" s="10" t="n"/>
       <c r="H20" s="10" t="n"/>
     </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>[insert technical details and result]</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="n"/>
-      <c r="C21" s="10" t="n"/>
-      <c r="D21" s="10" t="n"/>
-      <c r="E21" s="10" t="n"/>
-      <c r="F21" s="10" t="n"/>
-      <c r="G21" s="10" t="n"/>
-      <c r="H21" s="10" t="n"/>
-    </row>
-    <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="10" t="n"/>
-      <c r="B22" s="10" t="n"/>
-      <c r="C22" s="10" t="n"/>
-      <c r="D22" s="10" t="n"/>
-      <c r="E22" s="10" t="n"/>
-      <c r="F22" s="10" t="n"/>
-      <c r="G22" s="10" t="n"/>
-      <c r="H22" s="10" t="n"/>
-    </row>
-    <row r="23" ht="20" customHeight="1"/>
-    <row r="24" ht="20" customHeight="1"/>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Clubs &amp; Teams</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="n"/>
-      <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="n"/>
-      <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="n"/>
-      <c r="G25" s="7" t="n"/>
-      <c r="H25" s="7" t="n"/>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>[insert club/team role]</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="n"/>
-      <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="n"/>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>[insert dates]</t>
-        </is>
-      </c>
-      <c r="F26" s="9" t="n"/>
-      <c r="G26" s="9" t="n"/>
-      <c r="H26" s="9" t="n"/>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>[insert club/team name]</t>
-        </is>
-      </c>
+    <row r="21" ht="20" customHeight="1"/>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Heat Exchanger Lifecycle Analysis</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>2025 - 2026</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="n"/>
+      <c r="G22" s="9" t="n"/>
+      <c r="H22" s="9" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>AltaGas</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>Python, data analysis, technical assessment</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="n"/>
+      <c r="G23" s="9" t="n"/>
+      <c r="H23" s="9" t="n"/>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>Analyzed 2+ years of operating data for 12+ brazed aluminum heat exchangers to assess fatigue risk and monitoring gaps.</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="10" t="n"/>
+      <c r="D24" s="10" t="n"/>
+      <c r="E24" s="10" t="n"/>
+      <c r="F24" s="10" t="n"/>
+      <c r="G24" s="10" t="n"/>
+      <c r="H24" s="10" t="n"/>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="10" t="n"/>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="10" t="n"/>
+      <c r="F25" s="10" t="n"/>
+      <c r="G25" s="10" t="n"/>
+      <c r="H25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>Summarized lifecycle findings into practical recommendations for inspection planning and operating awareness.</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="10" t="n"/>
+      <c r="D26" s="10" t="n"/>
+      <c r="E26" s="10" t="n"/>
+      <c r="F26" s="10" t="n"/>
+      <c r="G26" s="10" t="n"/>
+      <c r="H26" s="10" t="n"/>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="10" t="n"/>
       <c r="B27" s="10" t="n"/>
       <c r="C27" s="10" t="n"/>
       <c r="D27" s="10" t="n"/>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>[insert subsystem, committee, or focus area]</t>
-        </is>
-      </c>
-      <c r="F27" s="9" t="n"/>
-      <c r="G27" s="9" t="n"/>
-      <c r="H27" s="9" t="n"/>
-    </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>[insert responsibility or technical contribution]</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="n"/>
-      <c r="C28" s="10" t="n"/>
-      <c r="D28" s="10" t="n"/>
-      <c r="E28" s="10" t="n"/>
-      <c r="F28" s="10" t="n"/>
-      <c r="G28" s="10" t="n"/>
-      <c r="H28" s="10" t="n"/>
-    </row>
-    <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="10" t="n"/>
-      <c r="B29" s="10" t="n"/>
-      <c r="C29" s="10" t="n"/>
-      <c r="D29" s="10" t="n"/>
-      <c r="E29" s="10" t="n"/>
-      <c r="F29" s="10" t="n"/>
-      <c r="G29" s="10" t="n"/>
-      <c r="H29" s="10" t="n"/>
-    </row>
-    <row r="30" ht="24" customHeight="1">
+      <c r="E27" s="10" t="n"/>
+      <c r="F27" s="10" t="n"/>
+      <c r="G27" s="10" t="n"/>
+      <c r="H27" s="10" t="n"/>
+    </row>
+    <row r="28" ht="20" customHeight="1"/>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>Control Panel Builds</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="n"/>
+      <c r="C29" s="8" t="n"/>
+      <c r="D29" s="8" t="n"/>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>Summer Terms, '23, '24</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="n"/>
+      <c r="G29" s="9" t="n"/>
+      <c r="H29" s="9" t="n"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>[insert teamwork, competition, or delivery outcome]</t>
+          <t>Spartan Controls</t>
         </is>
       </c>
       <c r="B30" s="10" t="n"/>
       <c r="C30" s="10" t="n"/>
       <c r="D30" s="10" t="n"/>
-      <c r="E30" s="10" t="n"/>
-      <c r="F30" s="10" t="n"/>
-      <c r="G30" s="10" t="n"/>
-      <c r="H30" s="10" t="n"/>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>Industrial controls and panel QA</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="n"/>
+      <c r="G30" s="9" t="n"/>
+      <c r="H30" s="9" t="n"/>
     </row>
     <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="10" t="n"/>
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>Built, wired, loaded, and checked a sample of 30+ electrical control panels across individual and team builds.</t>
+        </is>
+      </c>
       <c r="B31" s="10" t="n"/>
       <c r="C31" s="10" t="n"/>
       <c r="D31" s="10" t="n"/>
@@ -3661,36 +6827,420 @@
       <c r="G31" s="10" t="n"/>
       <c r="H31" s="10" t="n"/>
     </row>
-    <row r="32" ht="20" customHeight="1"/>
-    <row r="33" ht="20" customHeight="1"/>
-    <row r="34" ht="20" customHeight="1"/>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="10" t="n"/>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
+      <c r="G32" s="10" t="n"/>
+      <c r="H32" s="10" t="n"/>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>Used schematics, wiring standards, and pre-delivery quality checks to resolve deficiencies before customer delivery.</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="10" t="n"/>
+      <c r="G33" s="10" t="n"/>
+      <c r="H33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="10" t="n"/>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="10" t="n"/>
+      <c r="G34" s="10" t="n"/>
+      <c r="H34" s="10" t="n"/>
+    </row>
+    <row r="35" ht="20" customHeight="1"/>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>Leather Tool Carrier</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="n"/>
+      <c r="C36" s="8" t="n"/>
+      <c r="D36" s="8" t="n"/>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="n"/>
+      <c r="G36" s="9" t="n"/>
+      <c r="H36" s="9" t="n"/>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>Spartan Controls</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="10" t="n"/>
+      <c r="D37" s="10" t="n"/>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>Shop workflow tooling</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="n"/>
+      <c r="G37" s="9" t="n"/>
+      <c r="H37" s="9" t="n"/>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>Designed and built a leather tool carrier to keep common hand tools organized and accessible during panel assembly.</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
+      <c r="G38" s="10" t="n"/>
+      <c r="H38" s="10" t="n"/>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="10" t="n"/>
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="10" t="n"/>
+      <c r="D39" s="10" t="n"/>
+      <c r="E39" s="10" t="n"/>
+      <c r="F39" s="10" t="n"/>
+      <c r="G39" s="10" t="n"/>
+      <c r="H39" s="10" t="n"/>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>Turned a personal workflow problem into a durable shop aid for faster repeated work.</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="10" t="n"/>
+      <c r="G40" s="10" t="n"/>
+      <c r="H40" s="10" t="n"/>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="10" t="n"/>
+      <c r="B41" s="10" t="n"/>
+      <c r="C41" s="10" t="n"/>
+      <c r="D41" s="10" t="n"/>
+      <c r="E41" s="10" t="n"/>
+      <c r="F41" s="10" t="n"/>
+      <c r="G41" s="10" t="n"/>
+      <c r="H41" s="10" t="n"/>
+    </row>
+    <row r="42" ht="20" customHeight="1"/>
+    <row r="43" ht="20" customHeight="1"/>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>Clubs &amp; Teams</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="n"/>
+      <c r="C44" s="7" t="n"/>
+      <c r="D44" s="7" t="n"/>
+      <c r="E44" s="7" t="n"/>
+      <c r="F44" s="7" t="n"/>
+      <c r="G44" s="7" t="n"/>
+      <c r="H44" s="7" t="n"/>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>Formula EV Electrical Systems</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="n"/>
+      <c r="C45" s="8" t="n"/>
+      <c r="D45" s="8" t="n"/>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>Winter 2025 - Present</t>
+        </is>
+      </c>
+      <c r="F45" s="9" t="n"/>
+      <c r="G45" s="9" t="n"/>
+      <c r="H45" s="9" t="n"/>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>Formula EV Racing</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="n"/>
+      <c r="C46" s="10" t="n"/>
+      <c r="D46" s="10" t="n"/>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>Low-voltage electrical systems</t>
+        </is>
+      </c>
+      <c r="F46" s="9" t="n"/>
+      <c r="G46" s="9" t="n"/>
+      <c r="H46" s="9" t="n"/>
+    </row>
+    <row r="47" ht="24" customHeight="1">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>Coordinate low-voltage power distribution, sensor integration, and safety-interface planning around the UA27 vehicle package.</t>
+        </is>
+      </c>
+      <c r="B47" s="10" t="n"/>
+      <c r="C47" s="10" t="n"/>
+      <c r="D47" s="10" t="n"/>
+      <c r="E47" s="10" t="n"/>
+      <c r="F47" s="10" t="n"/>
+      <c r="G47" s="10" t="n"/>
+      <c r="H47" s="10" t="n"/>
+    </row>
+    <row r="48" ht="24" customHeight="1">
+      <c r="A48" s="10" t="n"/>
+      <c r="B48" s="10" t="n"/>
+      <c r="C48" s="10" t="n"/>
+      <c r="D48" s="10" t="n"/>
+      <c r="E48" s="10" t="n"/>
+      <c r="F48" s="10" t="n"/>
+      <c r="G48" s="10" t="n"/>
+      <c r="H48" s="10" t="n"/>
+    </row>
+    <row r="49" ht="24" customHeight="1">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>Work across mechanical and software constraints to make electrical systems accessible, serviceable, and competition-ready.</t>
+        </is>
+      </c>
+      <c r="B49" s="10" t="n"/>
+      <c r="C49" s="10" t="n"/>
+      <c r="D49" s="10" t="n"/>
+      <c r="E49" s="10" t="n"/>
+      <c r="F49" s="10" t="n"/>
+      <c r="G49" s="10" t="n"/>
+      <c r="H49" s="10" t="n"/>
+    </row>
+    <row r="50" ht="24" customHeight="1">
+      <c r="A50" s="10" t="n"/>
+      <c r="B50" s="10" t="n"/>
+      <c r="C50" s="10" t="n"/>
+      <c r="D50" s="10" t="n"/>
+      <c r="E50" s="10" t="n"/>
+      <c r="F50" s="10" t="n"/>
+      <c r="G50" s="10" t="n"/>
+      <c r="H50" s="10" t="n"/>
+    </row>
+    <row r="51" ht="20" customHeight="1"/>
+    <row r="52" ht="20" customHeight="1"/>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>Fabrication &amp; Materials</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="n"/>
+      <c r="C53" s="7" t="n"/>
+      <c r="D53" s="7" t="n"/>
+      <c r="E53" s="7" t="n"/>
+      <c r="F53" s="7" t="n"/>
+      <c r="G53" s="7" t="n"/>
+      <c r="H53" s="7" t="n"/>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>Composite Skateboard Decks</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="n"/>
+      <c r="C54" s="8" t="n"/>
+      <c r="D54" s="8" t="n"/>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t>Earlier build series</t>
+        </is>
+      </c>
+      <c r="F54" s="9" t="n"/>
+      <c r="G54" s="9" t="n"/>
+      <c r="H54" s="9" t="n"/>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>Personal Project</t>
+        </is>
+      </c>
+      <c r="B55" s="10" t="n"/>
+      <c r="C55" s="10" t="n"/>
+      <c r="D55" s="10" t="n"/>
+      <c r="E55" s="9" t="inlineStr">
+        <is>
+          <t>Lamination, fiberglass layups, embedded aluminum</t>
+        </is>
+      </c>
+      <c r="F55" s="9" t="n"/>
+      <c r="G55" s="9" t="n"/>
+      <c r="H55" s="9" t="n"/>
+    </row>
+    <row r="56" ht="24" customHeight="1">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>Built skateboard decks while learning lamination and fiberglass layup techniques, including one green deck with sealed-in aluminum.</t>
+        </is>
+      </c>
+      <c r="B56" s="10" t="n"/>
+      <c r="C56" s="10" t="n"/>
+      <c r="D56" s="10" t="n"/>
+      <c r="E56" s="10" t="n"/>
+      <c r="F56" s="10" t="n"/>
+      <c r="G56" s="10" t="n"/>
+      <c r="H56" s="10" t="n"/>
+    </row>
+    <row r="57" ht="24" customHeight="1">
+      <c r="A57" s="10" t="n"/>
+      <c r="B57" s="10" t="n"/>
+      <c r="C57" s="10" t="n"/>
+      <c r="D57" s="10" t="n"/>
+      <c r="E57" s="10" t="n"/>
+      <c r="F57" s="10" t="n"/>
+      <c r="G57" s="10" t="n"/>
+      <c r="H57" s="10" t="n"/>
+    </row>
+    <row r="58" ht="20" customHeight="1"/>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>Father's Day Knife Forging</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="n"/>
+      <c r="C59" s="8" t="n"/>
+      <c r="D59" s="8" t="n"/>
+      <c r="E59" s="9" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F59" s="9" t="n"/>
+      <c r="G59" s="9" t="n"/>
+      <c r="H59" s="9" t="n"/>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>Personal Project</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="n"/>
+      <c r="C60" s="10" t="n"/>
+      <c r="D60" s="10" t="n"/>
+      <c r="E60" s="9" t="inlineStr">
+        <is>
+          <t>Forging, heat, grinding, finishing</t>
+        </is>
+      </c>
+      <c r="F60" s="9" t="n"/>
+      <c r="G60" s="9" t="n"/>
+      <c r="H60" s="9" t="n"/>
+    </row>
+    <row r="61" ht="24" customHeight="1">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>Completed a knife forging project focused on shaping, heat response, grinding, and practical finish work.</t>
+        </is>
+      </c>
+      <c r="B61" s="10" t="n"/>
+      <c r="C61" s="10" t="n"/>
+      <c r="D61" s="10" t="n"/>
+      <c r="E61" s="10" t="n"/>
+      <c r="F61" s="10" t="n"/>
+      <c r="G61" s="10" t="n"/>
+      <c r="H61" s="10" t="n"/>
+    </row>
+    <row r="62" ht="24" customHeight="1">
+      <c r="A62" s="10" t="n"/>
+      <c r="B62" s="10" t="n"/>
+      <c r="C62" s="10" t="n"/>
+      <c r="D62" s="10" t="n"/>
+      <c r="E62" s="10" t="n"/>
+      <c r="F62" s="10" t="n"/>
+      <c r="G62" s="10" t="n"/>
+      <c r="H62" s="10" t="n"/>
+    </row>
+    <row r="63" ht="20" customHeight="1"/>
+    <row r="64" ht="20" customHeight="1"/>
+    <row r="65" ht="20" customHeight="1"/>
   </sheetData>
-  <mergeCells count="25">
-    <mergeCell ref="A17:D17"/>
+  <mergeCells count="53">
+    <mergeCell ref="A23:D23"/>
     <mergeCell ref="A12:H13"/>
-    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="E45:H45"/>
     <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A26:H27"/>
+    <mergeCell ref="A56:H57"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="E16:H16"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="E54:H54"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A14:H15"/>
-    <mergeCell ref="A21:H22"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="A17:H18"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="E18:H18"/>
+    <mergeCell ref="A33:H34"/>
     <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A47:H48"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A15:D15"/>
     <mergeCell ref="A10:H11"/>
+    <mergeCell ref="A59:D59"/>
     <mergeCell ref="A19:H20"/>
+    <mergeCell ref="E55:H55"/>
+    <mergeCell ref="A60:D60"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A38:H39"/>
+    <mergeCell ref="A45:D45"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="E17:H17"/>
-    <mergeCell ref="A28:H29"/>
+    <mergeCell ref="E23:H23"/>
     <mergeCell ref="E8:H8"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A31:H32"/>
+    <mergeCell ref="A49:H50"/>
+    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="E29:H29"/>
+    <mergeCell ref="A40:H41"/>
+    <mergeCell ref="A16:D16"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A30:H31"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="A24:H25"/>
+    <mergeCell ref="A61:H62"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="E60:H60"/>
     <mergeCell ref="E9:H9"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="A53:H53"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="E46:H46"/>
+    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="E59:H59"/>
+    <mergeCell ref="E36:H36"/>
   </mergeCells>
   <pageMargins left="0.35" right="0.35" top="0.35" bottom="0.35" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="1" fitToHeight="1" fitToWidth="1"/>
